--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ld_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ld_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>29-06-2021 08:30</t>
+          <t>2021-06-29 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>29-06-2021 08:30</t>
+          <t>2021-06-29 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
